--- a/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T08:45:28+00:00</t>
+    <t>2026-03-09T10:02:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T10:02:41+00:00</t>
+    <t>2026-03-09T11:03:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T11:03:31+00:00</t>
+    <t>2026-03-10T16:01:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T16:01:29+00:00</t>
+    <t>2026-03-11T10:08:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T10:08:51+00:00</t>
+    <t>2026-03-12T10:11:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T10:11:51+00:00</t>
+    <t>2026-03-12T16:00:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-12T16:00:43+00:00</t>
+    <t>2026-03-13T09:36:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T09:36:21+00:00</t>
+    <t>2026-03-13T11:22:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T11:22:36+00:00</t>
+    <t>2026-03-13T13:52:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T13:52:14+00:00</t>
+    <t>2026-03-17T16:51:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T16:51:37+00:00</t>
+    <t>2026-03-20T18:59:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T18:59:33+00:00</t>
+    <t>2026-03-24T09:38:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T09:38:58+00:00</t>
+    <t>2026-03-25T11:37:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T11:37:26+00:00</t>
+    <t>2026-03-25T15:18:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:18:47+00:00</t>
+    <t>2026-03-26T16:05:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-26T16:05:11+00:00</t>
+    <t>2026-03-27T09:46:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
+++ b/ig/DM-MARS-2026/ValueSet-vs-cipucd-all.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:46:53+00:00</t>
+    <t>2026-06-03T09:21:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
